--- a/stories/arbres/TREE-VIV-002.xlsx
+++ b/stories/arbres/TREE-VIV-002.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Adam se promène au marché, avec papa. Une caisse de paille. Un coq chante. Une poule picore. Un poussin suit. Papa dit : coq, poule, poussin. Ce sont trois noms de la famille. Adam répète les trois noms. Coq. Poule. Poussin. Ce sont des animaux. On dit les trois noms de la famille. On dit les trois noms de la famille. Coq, poule, poussin.</t>
+          <t>Adam se promène au marché, avec papa. Une caisse de paille. Un coq chante. Une poule picore. Un poussin suit. Coq, poule, poussin. Ce sont trois noms de la famille. Adam répète les trois noms. Coq. Poule. Poussin. Ce sont des animaux. On dit les trois noms de la famille. On dit les trois noms de la famille. Coq, poule, poussin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Adam se promène au marché, avec papa. Une caisse de paille. Un coq chante. Une poule picore. Un poussin suit.
+papa|Coq, poule, poussin. Ce sont trois noms de la famille.
+narrateur|Adam répète les trois noms. Coq. Poule. Poussin. Ce sont des animaux. On dit les trois noms de la famille. On dit les trois noms de la famille. Coq, poule, poussin.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1678,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Adam imagine le bac à sable. Dans le sable, des figurines. Un coq. Une poule. Un poussin. Papa dit les trois noms de la famille. Adam les dit aussi. Coq, poule, poussin. On dit les trois noms de la famille. Coq, poule, poussin.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1859,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Coq, poule, et le petit. Qui est le petit ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2032,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a dit les trois noms de la famille. Coq, poule, poussin. On dit les trois noms de la famille. Coq, poule, poussin.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2223,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2390,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Adam prend les cubes. La couverture est douce. Avec les cubes, Adam fait une petite ferme. Coq, poule, poussin. Trois noms de la famille. On dit les trois noms de la famille. Coq, poule, poussin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2529,6 +2583,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -2693,6 +2752,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton rouge. La lumière est claire. On pose les pieds par terre. On a dit les trois noms de la famille. Des animaux. Coq, poule, poussin. On dit les trois noms de la famille. Coq, poule, poussin. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2919,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3086,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton bleu. Des miettes dorment sur la table. On parle tout bas. On a dit les trois noms de la famille. Des animaux. Chat, chatte, chaton. On dit les trois noms de la famille. Coq, poule, poussin. Papa serre Adam tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3253,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3420,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton vert. Un chat miaule une fois. On range les jouets. On a dit les trois noms de la famille. Des animaux. Chien, chienne, chiot. On dit les trois noms de la famille. Coq, poule, poussin. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3587,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3754,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Adam prend le livre. Une pomme sent le sucré. Le livre montre un cheval, une jument, un poulain. Trois noms de la famille. Des animaux. On dit les trois noms de la famille. Coq, poule, poussin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3855,6 +3949,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3879,7 +3978,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Adam pose un jeton rouge. Les chaussures font toc toc. On s'assoit un moment. On a dit les trois noms de la famille. Des animaux. Cheval, jument, poulain. On dit les trois noms de la famille. Coq, poule, poussin. Adam range. Papa dit : c'est bien.</t>
+          <t>Adam pose un jeton rouge. Les chaussures font toc toc. On s'assoit un moment. On a dit les trois noms de la famille. Des animaux. Cheval, jument, poulain. On dit les trois noms de la famille. Coq, poule, poussin. Adam range. C'est bien.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4017,6 +4116,12 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton rouge. Les chaussures font toc toc. On s'assoit un moment. On a dit les trois noms de la famille. Des animaux. Cheval, jument, poulain. On dit les trois noms de la famille. Coq, poule, poussin. Adam range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4284,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4451,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton bleu. La couverture est douce. On respire, un, deux. On a dit les trois noms de la famille. Des animaux. Coq, poule, poussin. On dit les trois noms de la famille. Coq, poule, poussin. On souffle. Adam sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4618,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4785,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton vert. Une cloche tinte au loin. On referme le sac. On a dit les trois noms de la famille. Des animaux. Chat, chatte, chaton. On dit les trois noms de la famille. Coq, poule, poussin. Adam prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4952,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4851,7 +4981,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Adam prend la dînette. La couverture est douce. À la dînette, Adam pose trois bols. Papa dit : trois noms. Chat, chatte, chaton. On dit les trois noms de la famille. Coq, poule, poussin.</t>
+          <t>Adam prend la dînette. La couverture est douce. À la dînette, Adam pose trois bols. Trois noms. Chat, chatte, chaton. On dit les trois noms de la famille. Coq, poule, poussin.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -4989,6 +5119,12 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Adam prend la dînette. La couverture est douce. À la dînette, Adam pose trois bols.
+papa|Trois noms. Chat, chatte, chaton. On dit les trois noms de la famille. Coq, poule, poussin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5177,6 +5313,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -5341,6 +5482,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton rouge. Le bois sent le chaud. On essuie une miette. On a dit les trois noms de la famille. Des animaux. Chien, chienne, chiot. On dit les trois noms de la famille. Coq, poule, poussin. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5649,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5816,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton bleu. Une goutte tombe, ploc. On met le doudou près. On a dit les trois noms de la famille. Des animaux. Cheval, jument, poulain. On dit les trois noms de la famille. Coq, poule, poussin. Papa serre Adam tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5983,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6150,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton vert. Le savon sent la fleur. On lace les chaussures. On a dit les trois noms de la famille. Des animaux. Coq, poule, poussin. On dit les trois noms de la famille. Coq, poule, poussin. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6317,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6175,7 +6346,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Adam pense au toboggan. Sur un livre, un chat, une chatte, un chaton. Papa dit : trois noms de la famille. Chat, chatte, chaton. Ce sont des animaux. Adam répète les trois noms. On dit les trois noms de la famille. Coq, poule, poussin.</t>
+          <t>Adam pense au toboggan. Sur un livre, un chat, une chatte, un chaton. Trois noms de la famille. Chat, chatte, chaton. Ce sont des animaux. Adam répète les trois noms. On dit les trois noms de la famille. Coq, poule, poussin.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6313,6 +6484,13 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pense au toboggan. Sur un livre, un chat, une chatte, un chaton.
+papa|Trois noms de la famille. Chat, chatte, chaton. Ce sont des animaux.
+narrateur|Adam répète les trois noms. On dit les trois noms de la famille. Coq, poule, poussin.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6667,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Chat, chatte, chaton. On dit combien de noms ?</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6840,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Chat, chatte, chaton. Trois noms de la famille. Papa sourit. On dit les trois noms de la famille. Coq, poule, poussin.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7031,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7005,6 +7198,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Adam prend les cubes. Le coussin est moelleux. Les cubes tombent, toc. Adam dit encore : coq, poule, poussin. Les trois noms. On dit les trois noms de la famille. Coq, poule, poussin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7195,6 +7393,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7219,7 +7422,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Adam pose un jeton rouge. Le tissu est tout doux. On met le manteau. On a dit les trois noms de la famille. Des animaux. Chat, chatte, chaton. On dit les trois noms de la famille. Coq, poule, poussin. Adam range. Papa dit : c'est bien.</t>
+          <t>Adam pose un jeton rouge. Le tissu est tout doux. On met le manteau. On a dit les trois noms de la famille. Des animaux. Chat, chatte, chaton. On dit les trois noms de la famille. Coq, poule, poussin. Adam range. C'est bien.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7357,6 +7560,12 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton rouge. Le tissu est tout doux. On met le manteau. On a dit les trois noms de la famille. Des animaux. Chat, chatte, chaton. On dit les trois noms de la famille. Coq, poule, poussin. Adam range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7728,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7681,6 +7895,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton bleu. Une cuillère tinte. On boit une gorgée. On a dit les trois noms de la famille. Des animaux. Chien, chienne, chiot. On dit les trois noms de la famille. Coq, poule, poussin. On souffle. Adam sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8062,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8005,6 +8229,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton vert. Le sable est tiède. On feuillette le livre. On a dit les trois noms de la famille. Des animaux. Cheval, jument, poulain. On dit les trois noms de la famille. Coq, poule, poussin. Adam prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8396,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8329,6 +8563,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Adam prend le livre. Le lait est froid dans le verre. Adam tourne la page. Un chien, une chienne, un chiot. Trois noms de la famille. On dit les trois noms de la famille. Coq, poule, poussin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8517,6 +8756,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -8681,6 +8925,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton rouge. Un rire court, tout petit. On referme le livre. On a dit les trois noms de la famille. Des animaux. Coq, poule, poussin. On dit les trois noms de la famille. Coq, poule, poussin. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8843,6 +9092,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9005,6 +9259,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton bleu. Le papier froisse, chut. On pose le ballon. On a dit les trois noms de la famille. Des animaux. Chat, chatte, chaton. On dit les trois noms de la famille. Coq, poule, poussin. Papa serre Adam tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9167,6 +9426,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9329,6 +9593,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton vert. L'herbe chatouille le mollet. On secoue le sable. On a dit les trois noms de la famille. Des animaux. Chien, chienne, chiot. On dit les trois noms de la famille. Coq, poule, poussin. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9491,6 +9760,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9515,7 +9789,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Adam prend la dînette. La laine gratte un peu. Une petite tasse. Adam dit : poussin. Papa ajoute : trois noms de la famille. On dit les trois noms de la famille. Coq, poule, poussin.</t>
+          <t>Adam prend la dînette. La laine gratte un peu. Une petite tasse. Poussin. Papa ajoute : trois noms de la famille. On dit les trois noms de la famille. Coq, poule, poussin.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9653,6 +9927,12 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Adam prend la dînette. La laine gratte un peu. Une petite tasse.
+enfant-m|Poussin. Papa ajoute : trois noms de la famille. On dit les trois noms de la famille. Coq, poule, poussin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9843,6 +10123,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9867,7 +10152,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Adam pose un jeton rouge. Un pigeon roucoule. On caresse le tissu. On a dit les trois noms de la famille. Des animaux. Cheval, jument, poulain. On dit les trois noms de la famille. Coq, poule, poussin. Adam range. Papa dit : c'est bien.</t>
+          <t>Adam pose un jeton rouge. Un pigeon roucoule. On caresse le tissu. On a dit les trois noms de la famille. Des animaux. Cheval, jument, poulain. On dit les trois noms de la famille. Coq, poule, poussin. Adam range. C'est bien.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10005,6 +10290,12 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton rouge. Un pigeon roucoule. On caresse le tissu. On a dit les trois noms de la famille. Des animaux. Cheval, jument, poulain. On dit les trois noms de la famille. Coq, poule, poussin. Adam range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10167,6 +10458,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10329,6 +10625,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton bleu. La fenêtre vibre un peu. On tend la main. On a dit les trois noms de la famille. Des animaux. Coq, poule, poussin. On dit les trois noms de la famille. Coq, poule, poussin. On souffle. Adam sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10491,6 +10792,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10653,6 +10959,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton vert. Le lait est froid dans le verre. On chante un petit air. On a dit les trois noms de la famille. Des animaux. Chat, chatte, chaton. On dit les trois noms de la famille. Coq, poule, poussin. Adam prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10815,6 +11126,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10839,7 +11155,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Adam pense aux balançoires. Papa montre une image. Un chien, une chienne, un chiot. Trois noms de la famille. Adam dit : chien, chienne, chiot. Des animaux. On dit les trois noms de la famille. Coq, poule, poussin.</t>
+          <t>Adam pense aux balançoires. Papa montre une image. Un chien, une chienne, un chiot. Trois noms de la famille. Chien, chienne, chiot. Des animaux. On dit les trois noms de la famille. Coq, poule, poussin.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10977,6 +11293,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pense aux balançoires. Papa montre une image. Un chien, une chienne, un chiot. Trois noms de la famille.
+enfant-m|Chien, chienne, chiot. Des animaux. On dit les trois noms de la famille. Coq, poule, poussin.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11153,6 +11475,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Chien, chienne, et le petit. Qui est le petit ?</t>
         </is>
       </c>
     </row>
@@ -11321,6 +11648,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Chien, chienne, chiot. Adam a dit les trois noms. Des animaux. On dit les trois noms de la famille. Coq, poule, poussin.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11507,6 +11839,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11531,7 +11868,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Adam prend les cubes. Un grelot sonne. Adam empile un cube. Papa dit : encore les trois noms. Coq, poule, poussin. On dit les trois noms de la famille. Coq, poule, poussin.</t>
+          <t>Adam prend les cubes. Un grelot sonne. Adam empile un cube. Encore les trois noms. Coq, poule, poussin. On dit les trois noms de la famille. Coq, poule, poussin.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -11669,6 +12006,12 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Adam prend les cubes. Un grelot sonne. Adam empile un cube.
+papa|Encore les trois noms. Coq, poule, poussin. On dit les trois noms de la famille. Coq, poule, poussin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11857,6 +12200,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -12021,6 +12369,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton rouge. La corde du sac est rêche. On compte jusqu'à trois. On a dit les trois noms de la famille. Des animaux. Chien, chienne, chiot. On dit les trois noms de la famille. Coq, poule, poussin. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12183,6 +12536,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12345,6 +12703,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton bleu. Le savon mousse entre les doigts. On montre du doigt. On a dit les trois noms de la famille. Des animaux. Cheval, jument, poulain. On dit les trois noms de la famille. Coq, poule, poussin. Papa serre Adam tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12507,6 +12870,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12669,6 +13037,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton vert. Un ruisseau chante. On range la chaise. On a dit les trois noms de la famille. Des animaux. Coq, poule, poussin. On dit les trois noms de la famille. Coq, poule, poussin. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12831,6 +13204,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12993,6 +13371,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Adam prend le livre. La terre est un peu humide. Le livre sent le papier. Cheval, jument, poulain. Trois noms de la famille. On dit les trois noms de la famille. Coq, poule, poussin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13183,6 +13566,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13207,7 +13595,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Adam pose un jeton rouge. La laine gratte un peu. On range un objet. On a dit les trois noms de la famille. Des animaux. Chat, chatte, chaton. On dit les trois noms de la famille. Coq, poule, poussin. Adam range. Papa dit : c'est bien.</t>
+          <t>Adam pose un jeton rouge. La laine gratte un peu. On range un objet. On a dit les trois noms de la famille. Des animaux. Chat, chatte, chaton. On dit les trois noms de la famille. Coq, poule, poussin. Adam range. C'est bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13345,6 +13733,12 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton rouge. La laine gratte un peu. On range un objet. On a dit les trois noms de la famille. Des animaux. Chat, chatte, chaton. On dit les trois noms de la famille. Coq, poule, poussin. Adam range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13507,6 +13901,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13669,6 +14068,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton bleu. Un pain croustille. On se tient la main. On a dit les trois noms de la famille. Des animaux. Chien, chienne, chiot. On dit les trois noms de la famille. Coq, poule, poussin. On souffle. Adam sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13831,6 +14235,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13993,6 +14402,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton vert. Le savon glisse. On dit merci. On a dit les trois noms de la famille. Des animaux. Cheval, jument, poulain. On dit les trois noms de la famille. Coq, poule, poussin. Adam prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14155,6 +14569,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14317,6 +14736,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Adam prend la dînette. Un grelot sonne. Adam range la dînette. Papa répète : trois noms de la famille d'animaux. On dit les trois noms de la famille. Coq, poule, poussin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14505,6 +14929,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -14669,6 +15098,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton rouge. Une plume vole. On souffle doucement. On a dit les trois noms de la famille. Des animaux. Coq, poule, poussin. On dit les trois noms de la famille. Coq, poule, poussin. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14831,6 +15265,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14993,6 +15432,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton bleu. Le banc est lisse. On écoute jusqu'au bout. On a dit les trois noms de la famille. Des animaux. Chat, chatte, chaton. On dit les trois noms de la famille. Coq, poule, poussin. Papa serre Adam tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15155,6 +15599,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15317,6 +15766,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose un jeton vert. Un grelot sonne. On attend son tour. On a dit les trois noms de la famille. Des animaux. Chien, chienne, chiot. On dit les trois noms de la famille. Coq, poule, poussin. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15479,6 +15933,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15497,7 +15956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15570,6 +16029,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-VIV-002.xlsx
+++ b/stories/arbres/TREE-VIV-002.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Adam répète les trois noms. Coq. Poule. Poussin. Ce sont des animaux. On dit les trois noms de la famille. On dit les trois noms de la famille. Coq, poule, poussin.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1522,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1683,6 +1690,7 @@
           <t>narrateur|Adam imagine le bac à sable. Dans le sable, des figurines. Un coq. Une poule. Un poussin. Papa dit les trois noms de la famille. Adam les dit aussi. Coq, poule, poussin. On dit les trois noms de la famille. Coq, poule, poussin.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1866,6 +1874,7 @@
           <t>narrateur|Coq, poule, et le petit. Qui est le petit ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2037,6 +2046,7 @@
           <t>narrateur|Adam a dit les trois noms de la famille. Coq, poule, poussin. On dit les trois noms de la famille. Coq, poule, poussin.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2228,6 +2238,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2395,6 +2406,7 @@
           <t>narrateur|Adam prend les cubes. La couverture est douce. Avec les cubes, Adam fait une petite ferme. Coq, poule, poussin. Trois noms de la famille. On dit les trois noms de la famille. Coq, poule, poussin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2590,6 +2602,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2757,6 +2770,7 @@
           <t>narrateur|Adam pose un jeton rouge. La lumière est claire. On pose les pieds par terre. On a dit les trois noms de la famille. Des animaux. Coq, poule, poussin. On dit les trois noms de la famille. Coq, poule, poussin. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2924,6 +2938,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3091,6 +3106,7 @@
           <t>narrateur|Adam pose un jeton bleu. Des miettes dorment sur la table. On parle tout bas. On a dit les trois noms de la famille. Des animaux. Chat, chatte, chaton. On dit les trois noms de la famille. Coq, poule, poussin. Papa serre Adam tout doux.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3258,6 +3274,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3425,6 +3442,11 @@
           <t>narrateur|Adam pose un jeton vert. Un chat miaule une fois. On range les jouets. On a dit les trois noms de la famille. Des animaux. Chien, chienne, chiot. On dit les trois noms de la famille. Coq, poule, poussin. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3592,6 +3614,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3759,6 +3782,7 @@
           <t>narrateur|Adam prend le livre. Une pomme sent le sucré. Le livre montre un cheval, une jument, un poulain. Trois noms de la famille. Des animaux. On dit les trois noms de la famille. Coq, poule, poussin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3954,6 +3978,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4122,6 +4147,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4289,6 +4315,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4456,6 +4483,7 @@
           <t>narrateur|Adam pose un jeton bleu. La couverture est douce. On respire, un, deux. On a dit les trois noms de la famille. Des animaux. Coq, poule, poussin. On dit les trois noms de la famille. Coq, poule, poussin. On souffle. Adam sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4623,6 +4651,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4790,6 +4819,7 @@
           <t>narrateur|Adam pose un jeton vert. Une cloche tinte au loin. On referme le sac. On a dit les trois noms de la famille. Des animaux. Chat, chatte, chaton. On dit les trois noms de la famille. Coq, poule, poussin. Adam prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4957,6 +4987,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5125,6 +5156,7 @@
 papa|Trois noms. Chat, chatte, chaton. On dit les trois noms de la famille. Coq, poule, poussin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5320,6 +5352,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5487,6 +5520,11 @@
           <t>narrateur|Adam pose un jeton rouge. Le bois sent le chaud. On essuie une miette. On a dit les trois noms de la famille. Des animaux. Chien, chienne, chiot. On dit les trois noms de la famille. Coq, poule, poussin. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5654,6 +5692,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5821,6 +5860,7 @@
           <t>narrateur|Adam pose un jeton bleu. Une goutte tombe, ploc. On met le doudou près. On a dit les trois noms de la famille. Des animaux. Cheval, jument, poulain. On dit les trois noms de la famille. Coq, poule, poussin. Papa serre Adam tout doux.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5988,6 +6028,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6155,6 +6196,7 @@
           <t>narrateur|Adam pose un jeton vert. Le savon sent la fleur. On lace les chaussures. On a dit les trois noms de la famille. Des animaux. Coq, poule, poussin. On dit les trois noms de la famille. Coq, poule, poussin. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6322,6 +6364,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6491,6 +6534,7 @@
 narrateur|Adam répète les trois noms. On dit les trois noms de la famille. Coq, poule, poussin.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6674,6 +6718,7 @@
           <t>narrateur|Chat, chatte, chaton. On dit combien de noms ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6845,6 +6890,7 @@
           <t>narrateur|Chat, chatte, chaton. Trois noms de la famille. Papa sourit. On dit les trois noms de la famille. Coq, poule, poussin.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7036,6 +7082,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7203,6 +7250,7 @@
           <t>narrateur|Adam prend les cubes. Le coussin est moelleux. Les cubes tombent, toc. Adam dit encore : coq, poule, poussin. Les trois noms. On dit les trois noms de la famille. Coq, poule, poussin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7398,6 +7446,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7566,6 +7615,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7733,6 +7783,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7900,6 +7951,11 @@
           <t>narrateur|Adam pose un jeton bleu. Une cuillère tinte. On boit une gorgée. On a dit les trois noms de la famille. Des animaux. Chien, chienne, chiot. On dit les trois noms de la famille. Coq, poule, poussin. On souffle. Adam sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8067,6 +8123,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8234,6 +8291,7 @@
           <t>narrateur|Adam pose un jeton vert. Le sable est tiède. On feuillette le livre. On a dit les trois noms de la famille. Des animaux. Cheval, jument, poulain. On dit les trois noms de la famille. Coq, poule, poussin. Adam prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8401,6 +8459,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8568,6 +8627,11 @@
           <t>narrateur|Adam prend le livre. Le lait est froid dans le verre. Adam tourne la page. Un chien, une chienne, un chiot. Trois noms de la famille. On dit les trois noms de la famille. Coq, poule, poussin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8763,6 +8827,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8930,6 +8995,7 @@
           <t>narrateur|Adam pose un jeton rouge. Un rire court, tout petit. On referme le livre. On a dit les trois noms de la famille. Des animaux. Coq, poule, poussin. On dit les trois noms de la famille. Coq, poule, poussin. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9097,6 +9163,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9264,6 +9331,7 @@
           <t>narrateur|Adam pose un jeton bleu. Le papier froisse, chut. On pose le ballon. On a dit les trois noms de la famille. Des animaux. Chat, chatte, chaton. On dit les trois noms de la famille. Coq, poule, poussin. Papa serre Adam tout doux.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9431,6 +9499,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9598,6 +9667,11 @@
           <t>narrateur|Adam pose un jeton vert. L'herbe chatouille le mollet. On secoue le sable. On a dit les trois noms de la famille. Des animaux. Chien, chienne, chiot. On dit les trois noms de la famille. Coq, poule, poussin. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9765,6 +9839,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9933,6 +10008,7 @@
 enfant-m|Poussin. Papa ajoute : trois noms de la famille. On dit les trois noms de la famille. Coq, poule, poussin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10128,6 +10204,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10296,6 +10373,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10463,6 +10541,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10630,6 +10709,7 @@
           <t>narrateur|Adam pose un jeton bleu. La fenêtre vibre un peu. On tend la main. On a dit les trois noms de la famille. Des animaux. Coq, poule, poussin. On dit les trois noms de la famille. Coq, poule, poussin. On souffle. Adam sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10797,6 +10877,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10964,6 +11045,7 @@
           <t>narrateur|Adam pose un jeton vert. Le lait est froid dans le verre. On chante un petit air. On a dit les trois noms de la famille. Des animaux. Chat, chatte, chaton. On dit les trois noms de la famille. Coq, poule, poussin. Adam prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11131,6 +11213,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11299,6 +11382,11 @@
 enfant-m|Chien, chienne, chiot. Des animaux. On dit les trois noms de la famille. Coq, poule, poussin.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11480,6 +11568,11 @@
       <c r="AW61" t="inlineStr">
         <is>
           <t>narrateur|Chien, chienne, et le petit. Qui est le petit ?</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -11653,6 +11746,11 @@
           <t>narrateur|Chien, chienne, chiot. Adam a dit les trois noms. Des animaux. On dit les trois noms de la famille. Coq, poule, poussin.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11844,6 +11942,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12012,6 +12111,7 @@
 papa|Encore les trois noms. Coq, poule, poussin. On dit les trois noms de la famille. Coq, poule, poussin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12207,6 +12307,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12374,6 +12475,11 @@
           <t>narrateur|Adam pose un jeton rouge. La corde du sac est rêche. On compte jusqu'à trois. On a dit les trois noms de la famille. Des animaux. Chien, chienne, chiot. On dit les trois noms de la famille. Coq, poule, poussin. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12541,6 +12647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12708,6 +12815,7 @@
           <t>narrateur|Adam pose un jeton bleu. Le savon mousse entre les doigts. On montre du doigt. On a dit les trois noms de la famille. Des animaux. Cheval, jument, poulain. On dit les trois noms de la famille. Coq, poule, poussin. Papa serre Adam tout doux.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12875,6 +12983,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13042,6 +13151,7 @@
           <t>narrateur|Adam pose un jeton vert. Un ruisseau chante. On range la chaise. On a dit les trois noms de la famille. Des animaux. Coq, poule, poussin. On dit les trois noms de la famille. Coq, poule, poussin. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13209,6 +13319,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13376,6 +13487,7 @@
           <t>narrateur|Adam prend le livre. La terre est un peu humide. Le livre sent le papier. Cheval, jument, poulain. Trois noms de la famille. On dit les trois noms de la famille. Coq, poule, poussin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13571,6 +13683,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13739,6 +13852,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13906,6 +14020,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14073,6 +14188,11 @@
           <t>narrateur|Adam pose un jeton bleu. Un pain croustille. On se tient la main. On a dit les trois noms de la famille. Des animaux. Chien, chienne, chiot. On dit les trois noms de la famille. Coq, poule, poussin. On souffle. Adam sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14240,6 +14360,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14407,6 +14528,7 @@
           <t>narrateur|Adam pose un jeton vert. Le savon glisse. On dit merci. On a dit les trois noms de la famille. Des animaux. Cheval, jument, poulain. On dit les trois noms de la famille. Coq, poule, poussin. Adam prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14574,6 +14696,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14741,6 +14864,7 @@
           <t>narrateur|Adam prend la dînette. Un grelot sonne. Adam range la dînette. Papa répète : trois noms de la famille d'animaux. On dit les trois noms de la famille. Coq, poule, poussin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14936,6 +15060,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15103,6 +15228,7 @@
           <t>narrateur|Adam pose un jeton rouge. Une plume vole. On souffle doucement. On a dit les trois noms de la famille. Des animaux. Coq, poule, poussin. On dit les trois noms de la famille. Coq, poule, poussin. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15270,6 +15396,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15437,6 +15564,7 @@
           <t>narrateur|Adam pose un jeton bleu. Le banc est lisse. On écoute jusqu'au bout. On a dit les trois noms de la famille. Des animaux. Chat, chatte, chaton. On dit les trois noms de la famille. Coq, poule, poussin. Papa serre Adam tout doux.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15604,6 +15732,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15771,6 +15900,11 @@
           <t>narrateur|Adam pose un jeton vert. Un grelot sonne. On attend son tour. On a dit les trois noms de la famille. Des animaux. Chien, chienne, chiot. On dit les trois noms de la famille. Coq, poule, poussin. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15938,6 +16072,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15956,7 +16091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16036,6 +16171,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16050,7 +16199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16237,6 +16386,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
